--- a/scripts/qa-loop/artifacts/soroka/סקר חוזה - סורוקה — AI.xlsx
+++ b/scripts/qa-loop/artifacts/soroka/סקר חוזה - סורוקה — AI.xlsx
@@ -11,6 +11,177 @@
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: שיקום חדרי ניתוח צפוניים בבית חולים סורוקה (תנאים מיוחדים, ע׳21). מקור אחר: בניה מחדש של מתחם חדרי ניתוח צפוניים (מפרט טכני, ע׳1). מומלץ לאמת מול המקור. שם שונה במפרט טכני</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: בית חולים סורוקה - חדרי ניתוח צפוניים (תנאים מיוחדים, ע׳23). מקור אחר: מרכז רפואי סורוקה באר שבע (מפרט טכני, ע׳1). מומלץ לאמת מול המקור. שם שונה במפרט טכני</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: שירותי בריאות כללית, ח.פ 5899026114 (תנאים מיוחדים, ע׳36). מקור אחר: שרותי בריאות כללית (מפרט טכני, ע׳1). מומלץ לאמת מול המקור. שם שונה במפרט טכני</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: הקבלן חייב להגיש יומני עבודה, כתבי כמויות, חשבונות ופרוטוקולים באמצעות מערכת רמדורנט; הגשה מחוץ למערכת אינה תקפה (סעיף 8) (תנאים מיוחדים, ע׳26). מקור אחר: המהנדס מנהל יומן עבודה יומי עם פרטי עובדים, חומרים, ציוד, מזג אוויר, תקלות, הוראות ודיווחים; 4 עותקים, רכוש כללית, הקבלן רשאי להסתייג תוך 3 ימים (סעיף 6.5) (תנאים כלליים, ע׳49). מומלץ לאמת מול המקור. סעיף 8 בתנאים מיוחדים מול סעיף 6.5 בתנאים כלליים</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: לא ישולמו כל התייקרויות או הצמדה מכל סוג שהוא (סעיף 12.2.8 בתנאים הכלליים, חוזר במספר סעיפים) (תנאים מיוחדים, ע׳6). מקור אחר: הצמדה למדד מחירי התשומה בבניה למגורים/שע"ח; תקופה קובעת לפי לוח זמנים, חישוב הפרשי הצמדה בין מדד בסיס למדד חדש, תשלום על חשבונות חלקיים וסופי (סעיף 12.2) (תנאים כלליים, ע׳96). מומלץ לאמת מול המקור. סעיף 12.2.8 בתנאים מיוחדים מול סעיף 12.2 בתנאים כלליים</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C28" authorId="0">
+      <text>
+        <r>
+          <t>⚠ פריט מהותי — לא חולץ ערך מלא; יש לקרוא את הסעיף במקור ולאמת. יש לקרוא סעיף 12.2 (עמוד 96)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0">
+      <text>
+        <r>
+          <t>⚠ פריט מהותי — לא חולץ ערך מלא; יש לקרוא את הסעיף במקור ולאמת. יש לקרוא סעיף 12.2 (עמוד 96)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C31" authorId="0">
+      <text>
+        <r>
+          <t>⚠ מקור ספציפי גובר על מקור כללי. נבחר: שיעור חלקו של הקבלן בפרמיות בקשר לביטוח עבודות קבלניות יהיה 0.525% מסך כל מחיר העבודות (כולל מע"מ) נספח "ה". הקבלן יידרש לצרף אישור ביטוחים בנוסח המצורף (סעיף 6). (תנאים מיוחדים, ע׳25). מקור אחר: פוליסת ביטוח עבודות קבלניות כוללת נזק לעבודות ואחריות כלפי צד ג׳; הקבלן משתתף בפרמיה בשיעור הקובע מסך מחיר העבודות (סעיף 3.10.1–3.10.2). (תנאים כלליים, ע׳27). מומלץ לאמת מול המקור.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C34" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: תנאי התשלום יהיו 45 יום ממועד קבלת החשבון כנדרש בכללית. למעט האמור, כל סעיפי פרק 12 יחולו בשינויים המחויבים (סעיף 7.3). (תנאים מיוחדים, ע׳25). מקור אחר: תשלום חשבון חלקי מאושר תוך שוטף+93 יום; ניכוי סכום ההשתתפות בביטוח מהחשבון הראשון (סעיף 12.5, 3.10.2). (תנאים כלליים, ע׳102). מומלץ לאמת מול המקור. סעיף 7.3 בתנאים מיוחדים מול סעיף 12.5 בתנאים כלליים</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C40" authorId="0">
+      <text>
+        <r>
+          <t>⚠ מקור ספציפי גובר על מקור כללי. נבחר: ערבות ביצוע בנוסח נספח "א1" (סעיף 9.1) - ערוכה לטובת המזמין על ידי תאגיד בנקאי או חברת ביטוח מורשית, צמודה למדד מחירי התשומה בבניה למגורים, תקפה עד למועד שייקבע. (תנאים מיוחדים, ע׳26). מקור אחר: ערבות ביצוע 5% מסך מחיר העבודות + מע״מ, צמודה למדד; מוחזרת כנגד ערבויות בדק (סעיף 15.1.1). (תנאים כלליים, ע׳108). מומלץ לאמת מול המקור.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0">
+      <text>
+        <r>
+          <t>⚠ מקור ספציפי גובר על מקור כללי. נבחר: ערבות בדק בנוסח נספח "א2" (לתקופת האחריות – 24 חודשים ממועד מסירת הפרויקט למזמין) וערבות בדק לעבודות איטום בנוסח נספח "א3" (סעיף 9.1). (תנאים מיוחדים, ע׳26). מקור אחר: ערבות בדק 5% (או 10% לאיטום) מסכום החשבון הסופי + מע״מ; תוקף 24 חודשים או 5 שנים לאיטום (סעיף 15.1.3). (תנאים כלליים, ע׳109). מומלץ לאמת מול המקור.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: 24 חודשים ממועד מסירת הפרויקט (תנאים מיוחדים, ע׳26). מקור אחר: שנתיים לכל העבודות (למעט חריגים); שלוש שנים למכונות/מנועים/דוודים/אספלט/כבישים/מדרכות; חמש שנים לאיטום; תקופת התיישנות לשלד (סעיף 13.5) (תנאים כלליים, ע׳106). מומלץ לאמת מול המקור. 24 חודשים בתנאים מיוחדים מול שנתיים/עשר שנים במקורות אחרים</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C43" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: 24 חודשים ממועד מסירת הפרויקט (תנאים מיוחדים, ע׳26). מקור אחר: תקופת האחריות כמפורט בסעיף 13.5; אחריות גם לאחר תקופת הבדק אם הפגם נתגלה תוך 5 שנים (סעיף 13.5.4) (תנאים כלליים, ע׳106). מומלץ לאמת מול המקור. 24 חודשים בתנאים מיוחדים מול 12 חודשים/סעיף 13.5 במקורות אחרים</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0">
+      <text>
+        <r>
+          <t>⚠ פריט מהותי — לא חולץ ערך מלא; יש לקרוא את הסעיף במקור ולאמת. יש לקרוא סעיף 9.5 (עמוד 73)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C68" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: במקרה של סתירה בין התנאים הכלליים לבין התנאים המיוחדים יגבר האמור בתנאים המיוחדים (סעיף 1.2). (תנאים מיוחדים, ע׳23). מקור אחר: בסתירה בין תנאים כלליים למסמך אחר בחוזה — כוחו של המסמך האחר עדיף; המהנדס מכריע בסתירות בין תיאורים (סעיף 1.4) (תנאים כלליים, ע׳11). מומלץ לאמת מול המקור. סעיף 1.2 בתנאים מיוחדים מול סעיף 1.4 בתנאים כלליים</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C73" authorId="0">
+      <text>
+        <r>
+          <t>⚠ מקור ספציפי גובר על מקור כללי. נבחר: הקבלן אחראי למילוי מלא של הוראות פקודת הבטיחות בעבודה, תקנותיה וכל דין אחר, לרבות מינוי ממונה בטיחות, אספקת אמצעי בטיחות זמניים, גידור, שילוט, תאורה, קסדות ומעקות, והחלת נוהלי בטיחות לפי נספחים 3.1.1–3.1.12 בכל שלבי הביצוע ובתקופת האחריות (סעיפים 3.1.1–3.1.12). (תנאים כלליים, ע׳18). מקור אחר: עבודה בבית חולים פעיל 24/7 מחייבת תיאום מועדי ניתוק/התחברות למערכות (מים, חשמל, ביוב, תקשורת) רק באישור בכתב מהמפקח; חובה להחזיק אמצעי כיבוי אש תקינים, לבצע עבודות רעש</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -286,7 +457,7 @@
     <t>אופן הגשת חשבון ביניים:</t>
   </si>
   <si>
-    <t>הגשת חשבון חלקי בתחילת כל חודש עם דפי ריכוז, חשבון מצטבר, התיוקרויות, יומני עבודה וכל האישורים הנדרשים (סעיף 12.1.1).</t>
+    <t>הגשת חשבון חלקי בתחילת כל חודש עם דפי ריכוז, חשבון מצטבר, התייקרויות, יומני עבודה וכל האישורים הנדרשים (סעיף 12.1.1).</t>
   </si>
   <si>
     <t>תנאים כלליים — עמוד 91</t>
@@ -644,12 +815,27 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE9A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -721,13 +907,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
@@ -737,6 +926,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -762,12 +954,15 @@
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1196,962 +1391,962 @@
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>46023</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
     </row>
     <row r="6" ht="38.45" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="11"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="14">
         <v>1</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="15"/>
+      <c r="D7" s="17"/>
     </row>
     <row r="8" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="14">
         <v>3</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="14">
         <v>4</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="11" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="14">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
     </row>
     <row r="12" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="14">
         <v>6</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="17" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="A13" s="14">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+      <c r="A14" s="14">
         <v>8</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="17" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+      <c r="A15" s="14">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
+      <c r="A16" s="14">
         <v>10</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="17"/>
     </row>
     <row r="17" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
+      <c r="A17" s="14">
         <v>11</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
     </row>
     <row r="18" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
+      <c r="A18" s="14">
         <v>12</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
+      <c r="A19" s="14">
         <v>13</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
+      <c r="A20" s="14">
         <v>14</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="17" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
+      <c r="A21" s="14">
         <v>15</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="17"/>
     </row>
     <row r="22" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+      <c r="A22" s="14">
         <v>16</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="23" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+      <c r="A23" s="14">
         <v>17</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="17" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
+      <c r="A24" s="14">
         <v>18</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="25" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
+      <c r="A25" s="14">
         <v>19</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="17" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="26" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+      <c r="A26" s="14">
         <v>20</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="17"/>
     </row>
     <row r="27" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
+      <c r="A27" s="14">
         <v>21</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="28" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
+      <c r="A28" s="14">
         <v>22</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="29" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
+      <c r="A29" s="14">
         <v>23</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="30" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
+      <c r="A30" s="14">
         <v>24</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="17"/>
     </row>
     <row r="31" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
+      <c r="A31" s="14">
         <v>25</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
+      <c r="A32" s="14">
         <v>26</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="17" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="33" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
+      <c r="A33" s="14">
         <v>27</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="17"/>
     </row>
     <row r="34" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
+      <c r="A34" s="14">
         <v>28</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="17"/>
     </row>
     <row r="35" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
+      <c r="A35" s="14">
         <v>29</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="36" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="12">
+      <c r="A36" s="14">
         <v>30</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
+      <c r="A37" s="14">
         <v>31</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
     </row>
     <row r="38" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="12">
+      <c r="A38" s="14">
         <v>32</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="12">
+      <c r="A39" s="14">
         <v>33</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="17"/>
     </row>
     <row r="40" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="12">
+      <c r="A40" s="14">
         <v>34</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="17" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="41" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="12">
+      <c r="A41" s="14">
         <v>35</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="17" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="42" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="12">
+      <c r="A42" s="14">
         <v>36</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="17" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="43" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="12">
+      <c r="A43" s="14">
         <v>37</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="17" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="44" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="12">
+      <c r="A44" s="14">
         <v>38</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="17" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="45" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="12">
+      <c r="A45" s="14">
         <v>39</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="17" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="46" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
+      <c r="A46" s="14">
         <v>40</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="12">
+      <c r="A47" s="14">
         <v>41</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
     </row>
     <row r="48" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="12">
+      <c r="A48" s="14">
         <v>42</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="49" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="12">
+      <c r="A49" s="14">
         <v>43</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="17" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="50" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="12">
+      <c r="A50" s="14">
         <v>44</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="D50" s="17" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="51" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="12">
+      <c r="A51" s="14">
         <v>45</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="17" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="52" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="12">
+      <c r="A52" s="14">
         <v>46</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D52" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="53" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="12">
+      <c r="A53" s="14">
         <v>47</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="D53" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="54" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="12">
+      <c r="A54" s="14">
         <v>48</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="55" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="12">
+      <c r="A55" s="14">
         <v>49</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D55" s="17" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="56" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="12">
+      <c r="A56" s="14">
         <v>50</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="17" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="57" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="12">
+      <c r="A57" s="14">
         <v>51</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D57" s="17" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="58" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="12">
+      <c r="A58" s="14">
         <v>52</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="D58" s="17" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="59" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="12">
+      <c r="A59" s="14">
         <v>53</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
     </row>
     <row r="60" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="12">
+      <c r="A60" s="14">
         <v>54</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
     </row>
     <row r="61" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="12">
+      <c r="A61" s="14">
         <v>55</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D61" s="15" t="s">
+      <c r="D61" s="17" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="62" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="12">
+      <c r="A62" s="14">
         <v>56</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="C62" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D62" s="15" t="s">
+      <c r="D62" s="17" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="63" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="12">
+      <c r="A63" s="14">
         <v>57</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
     </row>
     <row r="64" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="12">
+      <c r="A64" s="14">
         <v>58</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="D64" s="17" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="65" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="12">
+      <c r="A65" s="14">
         <v>59</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D65" s="15" t="s">
+      <c r="D65" s="17" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="66" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="12">
+      <c r="A66" s="14">
         <v>60</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C66" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D66" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="67" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="12">
+      <c r="A67" s="14">
         <v>61</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
     </row>
     <row r="68" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="12">
+      <c r="A68" s="14">
         <v>62</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C68" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="69" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="12">
+      <c r="A69" s="14">
         <v>63</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
     </row>
     <row r="70" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="12">
+      <c r="A70" s="14">
         <v>64</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="D70" s="17" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="71" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="12">
+      <c r="A71" s="14">
         <v>65</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="D71" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="72" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="12">
+      <c r="A72" s="14">
         <v>66</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D72" s="15" t="s">
+      <c r="D72" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="73" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="12">
+      <c r="A73" s="14">
         <v>67</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="D73" s="15" t="s">
+      <c r="D73" s="17" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="74" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="12">
+      <c r="A74" s="14">
         <v>68</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C74" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" s="17" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="75" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="12">
+      <c r="A75" s="14">
         <v>69</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="D75" s="17" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="76" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="12">
+      <c r="A76" s="14">
         <v>70</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" s="17" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
+      <c r="B77" s="23"/>
+      <c r="C77" s="23"/>
+      <c r="D77" s="23"/>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
@@ -2189,6 +2384,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>